--- a/Rescource/Stage1.xlsx
+++ b/Rescource/Stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2590314 竹中 槙吾\ｱｲﾑﾚﾃﾞｨ\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5779529E-2409-44CD-9AC2-B8EBEC24A2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB9F144-5C01-4920-9A51-92E56BFAAE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="600" windowWidth="21000" windowHeight="14880" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Rescource/Stage1.xlsx
+++ b/Rescource/Stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5779529E-2409-44CD-9AC2-B8EBEC24A2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5138C30-AA2F-484A-AD4F-408F6D7370C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="600" windowWidth="21000" windowHeight="14880" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
+    <workbookView xWindow="7800" yWindow="0" windowWidth="21000" windowHeight="14880" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,56 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -130,26 +179,26 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor>
         <xdr:from>
-          <xdr:col>44</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
+          <xdr:col>42</xdr:col>
+          <xdr:colOff>123825</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>104775</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>48</xdr:col>
-          <xdr:colOff>142875</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
+          <xdr:col>54</xdr:col>
+          <xdr:colOff>228600</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1025" name="Button 1" hidden="1">
+            <xdr:cNvPr id="1026" name="Button 2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1025"/>
+                  <a14:compatExt spid="_x0000_s1026"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -185,7 +234,7 @@
                   <a:latin typeface="游ゴシック"/>
                   <a:ea typeface="游ゴシック"/>
                 </a:rPr>
-                <a:t>ボタン 1</a:t>
+                <a:t>ボタン 2</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -496,118 +545,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2AE116-0909-4068-9DE1-969012F66DCA}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:FF30"/>
+  <dimension ref="A1:KS30"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="3.5" bestFit="1" customWidth="1"/>
     <col min="107" max="107" width="3.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>1</v>
       </c>
-      <c r="FF1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="2" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="FF2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="FF3">
-        <v>1</v>
-      </c>
     </row>
-    <row r="4" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="FF4">
-        <v>1</v>
+      <c r="GX4">
+        <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="FF5">
+      <c r="GV5">
+        <v>1</v>
+      </c>
+      <c r="GW5">
+        <v>1</v>
+      </c>
+      <c r="GX5">
+        <v>1</v>
+      </c>
+      <c r="HE5">
+        <v>1</v>
+      </c>
+      <c r="HF5">
+        <v>1</v>
+      </c>
+      <c r="HG5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="FF6">
+      <c r="GV6">
+        <v>1</v>
+      </c>
+      <c r="GW6">
+        <v>1</v>
+      </c>
+      <c r="GX6">
+        <v>1</v>
+      </c>
+      <c r="HE6">
+        <v>1</v>
+      </c>
+      <c r="HF6">
+        <v>1</v>
+      </c>
+      <c r="HG6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="FF7">
+      <c r="GV7">
+        <v>1</v>
+      </c>
+      <c r="GW7">
+        <v>1</v>
+      </c>
+      <c r="GX7">
+        <v>1</v>
+      </c>
+      <c r="HE7">
+        <v>1</v>
+      </c>
+      <c r="HF7">
+        <v>1</v>
+      </c>
+      <c r="HG7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="FF8">
+      <c r="GS8">
+        <v>1</v>
+      </c>
+      <c r="GT8">
+        <v>1</v>
+      </c>
+      <c r="GU8">
+        <v>1</v>
+      </c>
+      <c r="GY8">
+        <v>1</v>
+      </c>
+      <c r="GZ8">
+        <v>1</v>
+      </c>
+      <c r="HA8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="FF9">
+      <c r="GS9">
+        <v>1</v>
+      </c>
+      <c r="GT9">
+        <v>1</v>
+      </c>
+      <c r="GU9">
+        <v>1</v>
+      </c>
+      <c r="GY9">
+        <v>1</v>
+      </c>
+      <c r="GZ9">
+        <v>1</v>
+      </c>
+      <c r="HA9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="FF10">
+      <c r="GS10">
+        <v>1</v>
+      </c>
+      <c r="GT10">
+        <v>1</v>
+      </c>
+      <c r="GU10">
+        <v>1</v>
+      </c>
+      <c r="GY10">
+        <v>1</v>
+      </c>
+      <c r="GZ10">
+        <v>1</v>
+      </c>
+      <c r="HA10">
+        <v>1</v>
+      </c>
+      <c r="HF10">
+        <v>1</v>
+      </c>
+      <c r="HG10">
+        <v>1</v>
+      </c>
+      <c r="HH10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1</v>
       </c>
-      <c r="FF11">
+      <c r="HF11">
+        <v>1</v>
+      </c>
+      <c r="HG11">
+        <v>1</v>
+      </c>
+      <c r="HH11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="FF12">
+      <c r="HF12">
+        <v>1</v>
+      </c>
+      <c r="HG12">
+        <v>1</v>
+      </c>
+      <c r="HH12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>1</v>
       </c>
-      <c r="FF13">
-        <v>1</v>
+      <c r="HD13">
+        <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>1</v>
       </c>
@@ -626,19 +777,130 @@
       <c r="AP14">
         <v>1</v>
       </c>
-      <c r="FF14">
-        <v>1</v>
+      <c r="GP14">
+        <v>1</v>
+      </c>
+      <c r="GQ14">
+        <v>1</v>
+      </c>
+      <c r="GR14">
+        <v>1</v>
+      </c>
+      <c r="GV14">
+        <v>1</v>
+      </c>
+      <c r="GW14">
+        <v>1</v>
+      </c>
+      <c r="GX14">
+        <v>1</v>
+      </c>
+      <c r="HB14">
+        <v>1</v>
+      </c>
+      <c r="HC14">
+        <v>1</v>
+      </c>
+      <c r="HD14">
+        <v>1</v>
+      </c>
+      <c r="IL14">
+        <v>3</v>
+      </c>
+      <c r="IV14">
+        <v>3</v>
+      </c>
+      <c r="JH14">
+        <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="FF15">
-        <v>1</v>
+      <c r="GP15">
+        <v>1</v>
+      </c>
+      <c r="GQ15">
+        <v>1</v>
+      </c>
+      <c r="GR15">
+        <v>1</v>
+      </c>
+      <c r="GV15">
+        <v>1</v>
+      </c>
+      <c r="GW15">
+        <v>1</v>
+      </c>
+      <c r="GX15">
+        <v>1</v>
+      </c>
+      <c r="HB15">
+        <v>1</v>
+      </c>
+      <c r="HC15">
+        <v>1</v>
+      </c>
+      <c r="HD15">
+        <v>1</v>
+      </c>
+      <c r="HV15">
+        <v>4</v>
+      </c>
+      <c r="IJ15">
+        <v>1</v>
+      </c>
+      <c r="IK15">
+        <v>1</v>
+      </c>
+      <c r="IL15">
+        <v>1</v>
+      </c>
+      <c r="IM15">
+        <v>1</v>
+      </c>
+      <c r="IN15">
+        <v>1</v>
+      </c>
+      <c r="IS15">
+        <v>1</v>
+      </c>
+      <c r="IT15">
+        <v>1</v>
+      </c>
+      <c r="IU15">
+        <v>1</v>
+      </c>
+      <c r="IV15">
+        <v>1</v>
+      </c>
+      <c r="IW15">
+        <v>1</v>
+      </c>
+      <c r="IX15">
+        <v>1</v>
+      </c>
+      <c r="JD15">
+        <v>1</v>
+      </c>
+      <c r="JE15">
+        <v>1</v>
+      </c>
+      <c r="JF15">
+        <v>1</v>
+      </c>
+      <c r="JG15">
+        <v>1</v>
+      </c>
+      <c r="JH15">
+        <v>1</v>
+      </c>
+      <c r="KJ15">
+        <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>1</v>
       </c>
@@ -654,19 +916,313 @@
       <c r="AH16">
         <v>1</v>
       </c>
-      <c r="FF16">
+      <c r="GP16">
+        <v>1</v>
+      </c>
+      <c r="GQ16">
+        <v>1</v>
+      </c>
+      <c r="GR16">
+        <v>1</v>
+      </c>
+      <c r="GU16">
+        <v>4</v>
+      </c>
+      <c r="GV16">
+        <v>1</v>
+      </c>
+      <c r="GW16">
+        <v>1</v>
+      </c>
+      <c r="GX16">
+        <v>1</v>
+      </c>
+      <c r="HB16">
+        <v>1</v>
+      </c>
+      <c r="HC16">
+        <v>1</v>
+      </c>
+      <c r="HD16">
+        <v>1</v>
+      </c>
+      <c r="HN16">
+        <v>1</v>
+      </c>
+      <c r="HO16">
+        <v>1</v>
+      </c>
+      <c r="HP16">
+        <v>1</v>
+      </c>
+      <c r="HQ16">
+        <v>1</v>
+      </c>
+      <c r="HR16">
+        <v>1</v>
+      </c>
+      <c r="HS16">
+        <v>1</v>
+      </c>
+      <c r="HT16">
+        <v>1</v>
+      </c>
+      <c r="HU16">
+        <v>1</v>
+      </c>
+      <c r="HV16">
+        <v>1</v>
+      </c>
+      <c r="HW16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1</v>
       </c>
-      <c r="FF17">
+      <c r="BK17">
+        <v>3</v>
+      </c>
+      <c r="GA17">
+        <v>1</v>
+      </c>
+      <c r="GB17">
+        <v>1</v>
+      </c>
+      <c r="GC17">
+        <v>1</v>
+      </c>
+      <c r="GD17">
+        <v>1</v>
+      </c>
+      <c r="GE17">
+        <v>1</v>
+      </c>
+      <c r="GF17">
+        <v>1</v>
+      </c>
+      <c r="GG17">
+        <v>1</v>
+      </c>
+      <c r="GH17">
+        <v>1</v>
+      </c>
+      <c r="GI17">
+        <v>1</v>
+      </c>
+      <c r="GJ17">
+        <v>1</v>
+      </c>
+      <c r="GK17">
+        <v>1</v>
+      </c>
+      <c r="GL17">
+        <v>1</v>
+      </c>
+      <c r="GM17">
+        <v>1</v>
+      </c>
+      <c r="GN17">
+        <v>1</v>
+      </c>
+      <c r="GO17">
+        <v>1</v>
+      </c>
+      <c r="GP17">
+        <v>1</v>
+      </c>
+      <c r="GQ17">
+        <v>1</v>
+      </c>
+      <c r="GR17">
+        <v>1</v>
+      </c>
+      <c r="GS17">
+        <v>1</v>
+      </c>
+      <c r="GT17">
+        <v>1</v>
+      </c>
+      <c r="GU17">
+        <v>1</v>
+      </c>
+      <c r="GV17">
+        <v>1</v>
+      </c>
+      <c r="GW17">
+        <v>1</v>
+      </c>
+      <c r="GX17">
+        <v>1</v>
+      </c>
+      <c r="GY17">
+        <v>1</v>
+      </c>
+      <c r="GZ17">
+        <v>1</v>
+      </c>
+      <c r="HA17">
+        <v>1</v>
+      </c>
+      <c r="HB17">
+        <v>1</v>
+      </c>
+      <c r="HC17">
+        <v>1</v>
+      </c>
+      <c r="HD17">
+        <v>1</v>
+      </c>
+      <c r="HE17">
+        <v>1</v>
+      </c>
+      <c r="HF17">
+        <v>1</v>
+      </c>
+      <c r="HG17">
+        <v>1</v>
+      </c>
+      <c r="HH17">
+        <v>1</v>
+      </c>
+      <c r="HI17">
+        <v>1</v>
+      </c>
+      <c r="HJ17">
+        <v>1</v>
+      </c>
+      <c r="HK17">
+        <v>1</v>
+      </c>
+      <c r="HL17">
+        <v>1</v>
+      </c>
+      <c r="HM17">
+        <v>1</v>
+      </c>
+      <c r="HN17">
+        <v>1</v>
+      </c>
+      <c r="HO17">
+        <v>1</v>
+      </c>
+      <c r="HP17">
+        <v>1</v>
+      </c>
+      <c r="HQ17">
+        <v>1</v>
+      </c>
+      <c r="HR17">
+        <v>1</v>
+      </c>
+      <c r="HS17">
+        <v>1</v>
+      </c>
+      <c r="HT17">
+        <v>1</v>
+      </c>
+      <c r="HU17">
+        <v>1</v>
+      </c>
+      <c r="HV17">
+        <v>1</v>
+      </c>
+      <c r="HW17">
+        <v>1</v>
+      </c>
+      <c r="HX17">
+        <v>1</v>
+      </c>
+      <c r="HY17">
+        <v>1</v>
+      </c>
+      <c r="HZ17">
+        <v>1</v>
+      </c>
+      <c r="IA17">
+        <v>1</v>
+      </c>
+      <c r="IB17">
+        <v>1</v>
+      </c>
+      <c r="IC17">
+        <v>1</v>
+      </c>
+      <c r="ID17">
+        <v>1</v>
+      </c>
+      <c r="IE17">
+        <v>1</v>
+      </c>
+      <c r="IF17">
+        <v>1</v>
+      </c>
+      <c r="JY17">
+        <v>1</v>
+      </c>
+      <c r="JZ17">
+        <v>1</v>
+      </c>
+      <c r="KA17">
+        <v>1</v>
+      </c>
+      <c r="KB17">
+        <v>1</v>
+      </c>
+      <c r="KC17">
+        <v>1</v>
+      </c>
+      <c r="KD17">
+        <v>1</v>
+      </c>
+      <c r="KE17">
+        <v>1</v>
+      </c>
+      <c r="KF17">
+        <v>1</v>
+      </c>
+      <c r="KG17">
+        <v>1</v>
+      </c>
+      <c r="KH17">
+        <v>1</v>
+      </c>
+      <c r="KI17">
+        <v>1</v>
+      </c>
+      <c r="KJ17">
+        <v>1</v>
+      </c>
+      <c r="KK17">
+        <v>1</v>
+      </c>
+      <c r="KL17">
+        <v>1</v>
+      </c>
+      <c r="KM17">
+        <v>1</v>
+      </c>
+      <c r="KN17">
+        <v>1</v>
+      </c>
+      <c r="KO17">
+        <v>1</v>
+      </c>
+      <c r="KP17">
+        <v>1</v>
+      </c>
+      <c r="KQ17">
+        <v>1</v>
+      </c>
+      <c r="KR17">
+        <v>1</v>
+      </c>
+      <c r="KS17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>1</v>
       </c>
@@ -706,19 +1262,385 @@
       <c r="BL18">
         <v>1</v>
       </c>
-      <c r="FF18">
+      <c r="GA18">
+        <v>1</v>
+      </c>
+      <c r="GB18">
+        <v>1</v>
+      </c>
+      <c r="GC18">
+        <v>1</v>
+      </c>
+      <c r="GD18">
+        <v>1</v>
+      </c>
+      <c r="GE18">
+        <v>1</v>
+      </c>
+      <c r="GF18">
+        <v>1</v>
+      </c>
+      <c r="GG18">
+        <v>1</v>
+      </c>
+      <c r="GH18">
+        <v>1</v>
+      </c>
+      <c r="GI18">
+        <v>1</v>
+      </c>
+      <c r="GJ18">
+        <v>1</v>
+      </c>
+      <c r="GK18">
+        <v>1</v>
+      </c>
+      <c r="GL18">
+        <v>1</v>
+      </c>
+      <c r="GM18">
+        <v>1</v>
+      </c>
+      <c r="GN18">
+        <v>1</v>
+      </c>
+      <c r="GO18">
+        <v>1</v>
+      </c>
+      <c r="GP18">
+        <v>1</v>
+      </c>
+      <c r="GQ18">
+        <v>1</v>
+      </c>
+      <c r="GR18">
+        <v>1</v>
+      </c>
+      <c r="GS18">
+        <v>1</v>
+      </c>
+      <c r="GT18">
+        <v>1</v>
+      </c>
+      <c r="GU18">
+        <v>1</v>
+      </c>
+      <c r="GV18">
+        <v>1</v>
+      </c>
+      <c r="GW18">
+        <v>1</v>
+      </c>
+      <c r="GX18">
+        <v>1</v>
+      </c>
+      <c r="GY18">
+        <v>1</v>
+      </c>
+      <c r="GZ18">
+        <v>1</v>
+      </c>
+      <c r="HA18">
+        <v>1</v>
+      </c>
+      <c r="HB18">
+        <v>1</v>
+      </c>
+      <c r="HC18">
+        <v>1</v>
+      </c>
+      <c r="HD18">
+        <v>1</v>
+      </c>
+      <c r="HE18">
+        <v>1</v>
+      </c>
+      <c r="HF18">
+        <v>1</v>
+      </c>
+      <c r="HG18">
+        <v>1</v>
+      </c>
+      <c r="HH18">
+        <v>1</v>
+      </c>
+      <c r="HI18">
+        <v>1</v>
+      </c>
+      <c r="HJ18">
+        <v>1</v>
+      </c>
+      <c r="HK18">
+        <v>1</v>
+      </c>
+      <c r="HL18">
+        <v>1</v>
+      </c>
+      <c r="HM18">
+        <v>1</v>
+      </c>
+      <c r="HN18">
+        <v>1</v>
+      </c>
+      <c r="HO18">
+        <v>1</v>
+      </c>
+      <c r="HP18">
+        <v>1</v>
+      </c>
+      <c r="HQ18">
+        <v>1</v>
+      </c>
+      <c r="HR18">
+        <v>1</v>
+      </c>
+      <c r="HS18">
+        <v>1</v>
+      </c>
+      <c r="HT18">
+        <v>1</v>
+      </c>
+      <c r="HU18">
+        <v>1</v>
+      </c>
+      <c r="HV18">
+        <v>1</v>
+      </c>
+      <c r="HW18">
+        <v>1</v>
+      </c>
+      <c r="HX18">
+        <v>1</v>
+      </c>
+      <c r="HY18">
+        <v>1</v>
+      </c>
+      <c r="HZ18">
+        <v>1</v>
+      </c>
+      <c r="IA18">
+        <v>1</v>
+      </c>
+      <c r="IB18">
+        <v>1</v>
+      </c>
+      <c r="IC18">
+        <v>1</v>
+      </c>
+      <c r="ID18">
+        <v>1</v>
+      </c>
+      <c r="IE18">
+        <v>1</v>
+      </c>
+      <c r="IF18">
+        <v>1</v>
+      </c>
+      <c r="JU18">
+        <v>1</v>
+      </c>
+      <c r="JV18">
+        <v>1</v>
+      </c>
+      <c r="JW18">
+        <v>1</v>
+      </c>
+      <c r="JX18">
+        <v>1</v>
+      </c>
+      <c r="JY18">
+        <v>1</v>
+      </c>
+      <c r="JZ18">
+        <v>1</v>
+      </c>
+      <c r="KA18">
+        <v>1</v>
+      </c>
+      <c r="KB18">
+        <v>1</v>
+      </c>
+      <c r="KC18">
+        <v>1</v>
+      </c>
+      <c r="KD18">
+        <v>1</v>
+      </c>
+      <c r="KE18">
+        <v>1</v>
+      </c>
+      <c r="KF18">
+        <v>1</v>
+      </c>
+      <c r="KG18">
+        <v>1</v>
+      </c>
+      <c r="KH18">
+        <v>1</v>
+      </c>
+      <c r="KI18">
+        <v>1</v>
+      </c>
+      <c r="KJ18">
+        <v>1</v>
+      </c>
+      <c r="KK18">
+        <v>1</v>
+      </c>
+      <c r="KL18">
+        <v>1</v>
+      </c>
+      <c r="KM18">
+        <v>1</v>
+      </c>
+      <c r="KN18">
+        <v>1</v>
+      </c>
+      <c r="KO18">
+        <v>1</v>
+      </c>
+      <c r="KP18">
+        <v>1</v>
+      </c>
+      <c r="KQ18">
+        <v>1</v>
+      </c>
+      <c r="KR18">
+        <v>1</v>
+      </c>
+      <c r="KS18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1</v>
       </c>
-      <c r="FF19">
+      <c r="GV19">
+        <v>1</v>
+      </c>
+      <c r="GW19">
+        <v>1</v>
+      </c>
+      <c r="GX19">
+        <v>1</v>
+      </c>
+      <c r="GY19">
+        <v>1</v>
+      </c>
+      <c r="GZ19">
+        <v>1</v>
+      </c>
+      <c r="HA19">
+        <v>1</v>
+      </c>
+      <c r="HB19">
+        <v>1</v>
+      </c>
+      <c r="HC19">
+        <v>1</v>
+      </c>
+      <c r="HD19">
+        <v>1</v>
+      </c>
+      <c r="HE19">
+        <v>1</v>
+      </c>
+      <c r="HF19">
+        <v>1</v>
+      </c>
+      <c r="HG19">
+        <v>1</v>
+      </c>
+      <c r="HH19">
+        <v>1</v>
+      </c>
+      <c r="JR19">
+        <v>1</v>
+      </c>
+      <c r="JS19">
+        <v>1</v>
+      </c>
+      <c r="JT19">
+        <v>1</v>
+      </c>
+      <c r="JU19">
+        <v>1</v>
+      </c>
+      <c r="JV19">
+        <v>1</v>
+      </c>
+      <c r="JW19">
+        <v>1</v>
+      </c>
+      <c r="JX19">
+        <v>1</v>
+      </c>
+      <c r="JY19">
+        <v>1</v>
+      </c>
+      <c r="JZ19">
+        <v>1</v>
+      </c>
+      <c r="KA19">
+        <v>1</v>
+      </c>
+      <c r="KB19">
+        <v>1</v>
+      </c>
+      <c r="KC19">
+        <v>1</v>
+      </c>
+      <c r="KD19">
+        <v>1</v>
+      </c>
+      <c r="KE19">
+        <v>1</v>
+      </c>
+      <c r="KF19">
+        <v>1</v>
+      </c>
+      <c r="KG19">
+        <v>1</v>
+      </c>
+      <c r="KH19">
+        <v>1</v>
+      </c>
+      <c r="KI19">
+        <v>1</v>
+      </c>
+      <c r="KJ19">
+        <v>1</v>
+      </c>
+      <c r="KK19">
+        <v>1</v>
+      </c>
+      <c r="KL19">
+        <v>1</v>
+      </c>
+      <c r="KM19">
+        <v>1</v>
+      </c>
+      <c r="KN19">
+        <v>1</v>
+      </c>
+      <c r="KO19">
+        <v>1</v>
+      </c>
+      <c r="KP19">
+        <v>1</v>
+      </c>
+      <c r="KQ19">
+        <v>1</v>
+      </c>
+      <c r="KR19">
+        <v>1</v>
+      </c>
+      <c r="KS19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>1</v>
       </c>
@@ -731,19 +1653,136 @@
       <c r="AD20">
         <v>1</v>
       </c>
-      <c r="FF20">
+      <c r="FR20">
+        <v>3</v>
+      </c>
+      <c r="GW20">
+        <v>1</v>
+      </c>
+      <c r="GX20">
+        <v>1</v>
+      </c>
+      <c r="GY20">
+        <v>1</v>
+      </c>
+      <c r="GZ20">
+        <v>1</v>
+      </c>
+      <c r="HA20">
+        <v>1</v>
+      </c>
+      <c r="HB20">
+        <v>1</v>
+      </c>
+      <c r="HC20">
+        <v>1</v>
+      </c>
+      <c r="HD20">
+        <v>1</v>
+      </c>
+      <c r="HE20">
+        <v>1</v>
+      </c>
+      <c r="HF20">
+        <v>1</v>
+      </c>
+      <c r="HG20">
+        <v>1</v>
+      </c>
+      <c r="JP20">
+        <v>1</v>
+      </c>
+      <c r="JQ20">
+        <v>1</v>
+      </c>
+      <c r="JR20">
+        <v>1</v>
+      </c>
+      <c r="JS20">
+        <v>1</v>
+      </c>
+      <c r="JT20">
+        <v>1</v>
+      </c>
+      <c r="JU20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>1</v>
       </c>
-      <c r="FF21">
+      <c r="FP21">
+        <v>1</v>
+      </c>
+      <c r="FQ21">
+        <v>1</v>
+      </c>
+      <c r="FR21">
+        <v>1</v>
+      </c>
+      <c r="FS21">
+        <v>1</v>
+      </c>
+      <c r="FT21">
+        <v>1</v>
+      </c>
+      <c r="FU21">
+        <v>1</v>
+      </c>
+      <c r="FV21">
+        <v>1</v>
+      </c>
+      <c r="GX21">
+        <v>1</v>
+      </c>
+      <c r="GY21">
+        <v>1</v>
+      </c>
+      <c r="GZ21">
+        <v>1</v>
+      </c>
+      <c r="HA21">
+        <v>1</v>
+      </c>
+      <c r="HB21">
+        <v>1</v>
+      </c>
+      <c r="HC21">
+        <v>1</v>
+      </c>
+      <c r="HD21">
+        <v>1</v>
+      </c>
+      <c r="HE21">
+        <v>1</v>
+      </c>
+      <c r="HF21">
+        <v>1</v>
+      </c>
+      <c r="JM21">
+        <v>3</v>
+      </c>
+      <c r="JN21">
+        <v>1</v>
+      </c>
+      <c r="JO21">
+        <v>1</v>
+      </c>
+      <c r="JP21">
+        <v>1</v>
+      </c>
+      <c r="JQ21">
+        <v>1</v>
+      </c>
+      <c r="JR21">
+        <v>1</v>
+      </c>
+      <c r="JS21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>1</v>
       </c>
@@ -771,14 +1810,56 @@
       <c r="BU22">
         <v>1</v>
       </c>
-      <c r="FF22">
+      <c r="DJ22">
+        <v>5</v>
+      </c>
+      <c r="GY22">
+        <v>1</v>
+      </c>
+      <c r="GZ22">
+        <v>1</v>
+      </c>
+      <c r="HA22">
+        <v>1</v>
+      </c>
+      <c r="HB22">
+        <v>1</v>
+      </c>
+      <c r="HC22">
+        <v>1</v>
+      </c>
+      <c r="HD22">
+        <v>1</v>
+      </c>
+      <c r="HE22">
+        <v>1</v>
+      </c>
+      <c r="JL22">
+        <v>1</v>
+      </c>
+      <c r="JM22">
+        <v>1</v>
+      </c>
+      <c r="JN22">
+        <v>1</v>
+      </c>
+      <c r="JO22">
+        <v>1</v>
+      </c>
+      <c r="JP22">
+        <v>1</v>
+      </c>
+      <c r="JQ22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>1</v>
       </c>
+      <c r="CM23">
+        <v>4</v>
+      </c>
       <c r="DG23">
         <v>1</v>
       </c>
@@ -794,11 +1875,41 @@
       <c r="DK23">
         <v>1</v>
       </c>
-      <c r="FF23">
+      <c r="GZ23">
+        <v>1</v>
+      </c>
+      <c r="HA23">
+        <v>1</v>
+      </c>
+      <c r="HB23">
+        <v>1</v>
+      </c>
+      <c r="HC23">
+        <v>1</v>
+      </c>
+      <c r="HD23">
+        <v>1</v>
+      </c>
+      <c r="JJ23">
+        <v>1</v>
+      </c>
+      <c r="JK23">
+        <v>1</v>
+      </c>
+      <c r="JL23">
+        <v>1</v>
+      </c>
+      <c r="JM23">
+        <v>1</v>
+      </c>
+      <c r="JN23">
+        <v>1</v>
+      </c>
+      <c r="JO23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>1</v>
       </c>
@@ -832,11 +1943,35 @@
       <c r="CN24">
         <v>1</v>
       </c>
-      <c r="FF24">
+      <c r="HA24">
+        <v>1</v>
+      </c>
+      <c r="HB24">
+        <v>1</v>
+      </c>
+      <c r="HC24">
+        <v>1</v>
+      </c>
+      <c r="JH24">
+        <v>1</v>
+      </c>
+      <c r="JI24">
+        <v>1</v>
+      </c>
+      <c r="JJ24">
+        <v>1</v>
+      </c>
+      <c r="JK24">
+        <v>1</v>
+      </c>
+      <c r="JL24">
+        <v>1</v>
+      </c>
+      <c r="JM24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>1</v>
       </c>
@@ -900,11 +2035,53 @@
       <c r="DC25">
         <v>1</v>
       </c>
-      <c r="FF25">
+      <c r="FH25">
+        <v>1</v>
+      </c>
+      <c r="FI25">
+        <v>1</v>
+      </c>
+      <c r="FJ25">
+        <v>1</v>
+      </c>
+      <c r="FK25">
+        <v>1</v>
+      </c>
+      <c r="FL25">
+        <v>1</v>
+      </c>
+      <c r="FM25">
+        <v>1</v>
+      </c>
+      <c r="GL25">
+        <v>1</v>
+      </c>
+      <c r="II25">
+        <v>4</v>
+      </c>
+      <c r="JE25">
+        <v>3</v>
+      </c>
+      <c r="JF25">
+        <v>1</v>
+      </c>
+      <c r="JG25">
+        <v>1</v>
+      </c>
+      <c r="JH25">
+        <v>1</v>
+      </c>
+      <c r="JI25">
+        <v>1</v>
+      </c>
+      <c r="JJ25">
+        <v>1</v>
+      </c>
+      <c r="JK25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>1</v>
       </c>
@@ -935,6 +2112,9 @@
       <c r="AV26">
         <v>1</v>
       </c>
+      <c r="BE26">
+        <v>3</v>
+      </c>
       <c r="CE26">
         <v>1</v>
       </c>
@@ -992,11 +2172,53 @@
       <c r="DW26">
         <v>1</v>
       </c>
-      <c r="FF26">
+      <c r="GJ26">
+        <v>1</v>
+      </c>
+      <c r="GL26">
+        <v>1</v>
+      </c>
+      <c r="GN26">
+        <v>1</v>
+      </c>
+      <c r="GP26">
+        <v>3</v>
+      </c>
+      <c r="HK26">
+        <v>1</v>
+      </c>
+      <c r="IB26">
+        <v>1</v>
+      </c>
+      <c r="IG26">
+        <v>1</v>
+      </c>
+      <c r="IH26">
+        <v>1</v>
+      </c>
+      <c r="II26">
+        <v>1</v>
+      </c>
+      <c r="JD26">
+        <v>1</v>
+      </c>
+      <c r="JE26">
+        <v>1</v>
+      </c>
+      <c r="JF26">
+        <v>1</v>
+      </c>
+      <c r="JG26">
+        <v>1</v>
+      </c>
+      <c r="JH26">
+        <v>1</v>
+      </c>
+      <c r="JI26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>1</v>
       </c>
@@ -1117,11 +2339,80 @@
       <c r="EF27">
         <v>1</v>
       </c>
-      <c r="FF27">
+      <c r="GH27">
+        <v>1</v>
+      </c>
+      <c r="GJ27">
+        <v>1</v>
+      </c>
+      <c r="GL27">
+        <v>1</v>
+      </c>
+      <c r="GN27">
+        <v>1</v>
+      </c>
+      <c r="GP27">
+        <v>1</v>
+      </c>
+      <c r="HK27">
+        <v>1</v>
+      </c>
+      <c r="HL27">
+        <v>1</v>
+      </c>
+      <c r="HM27">
+        <v>1</v>
+      </c>
+      <c r="HN27">
+        <v>1</v>
+      </c>
+      <c r="HP27">
+        <v>4</v>
+      </c>
+      <c r="HW27">
+        <v>5</v>
+      </c>
+      <c r="HY27">
+        <v>1</v>
+      </c>
+      <c r="HZ27">
+        <v>1</v>
+      </c>
+      <c r="IA27">
+        <v>1</v>
+      </c>
+      <c r="IB27">
+        <v>1</v>
+      </c>
+      <c r="IG27">
+        <v>1</v>
+      </c>
+      <c r="IH27">
+        <v>1</v>
+      </c>
+      <c r="II27">
+        <v>1</v>
+      </c>
+      <c r="JB27">
+        <v>1</v>
+      </c>
+      <c r="JC27">
+        <v>1</v>
+      </c>
+      <c r="JD27">
+        <v>1</v>
+      </c>
+      <c r="JE27">
+        <v>1</v>
+      </c>
+      <c r="JF27">
+        <v>1</v>
+      </c>
+      <c r="JG27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>1</v>
       </c>
@@ -1266,11 +2557,107 @@
       <c r="EF28">
         <v>1</v>
       </c>
-      <c r="FF28">
+      <c r="EZ28">
+        <v>3</v>
+      </c>
+      <c r="FW28">
+        <v>3</v>
+      </c>
+      <c r="GF28">
+        <v>1</v>
+      </c>
+      <c r="GH28">
+        <v>1</v>
+      </c>
+      <c r="GJ28">
+        <v>1</v>
+      </c>
+      <c r="GL28">
+        <v>1</v>
+      </c>
+      <c r="GN28">
+        <v>1</v>
+      </c>
+      <c r="GP28">
+        <v>1</v>
+      </c>
+      <c r="GR28">
+        <v>1</v>
+      </c>
+      <c r="HG28">
+        <v>3</v>
+      </c>
+      <c r="HK28">
+        <v>1</v>
+      </c>
+      <c r="HL28">
+        <v>1</v>
+      </c>
+      <c r="HM28">
+        <v>1</v>
+      </c>
+      <c r="HN28">
+        <v>1</v>
+      </c>
+      <c r="HO28">
+        <v>1</v>
+      </c>
+      <c r="HP28">
+        <v>1</v>
+      </c>
+      <c r="HQ28">
+        <v>1</v>
+      </c>
+      <c r="HV28">
+        <v>1</v>
+      </c>
+      <c r="HW28">
+        <v>1</v>
+      </c>
+      <c r="HX28">
+        <v>1</v>
+      </c>
+      <c r="HY28">
+        <v>1</v>
+      </c>
+      <c r="HZ28">
+        <v>1</v>
+      </c>
+      <c r="IA28">
+        <v>1</v>
+      </c>
+      <c r="IB28">
+        <v>1</v>
+      </c>
+      <c r="IG28">
+        <v>1</v>
+      </c>
+      <c r="IH28">
+        <v>1</v>
+      </c>
+      <c r="II28">
+        <v>1</v>
+      </c>
+      <c r="IZ28">
+        <v>1</v>
+      </c>
+      <c r="JA28">
+        <v>1</v>
+      </c>
+      <c r="JB28">
+        <v>1</v>
+      </c>
+      <c r="JC28">
+        <v>1</v>
+      </c>
+      <c r="JD28">
+        <v>1</v>
+      </c>
+      <c r="JE28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>1</v>
       </c>
@@ -1292,6 +2679,9 @@
       <c r="G29">
         <v>1</v>
       </c>
+      <c r="X29">
+        <v>3</v>
+      </c>
       <c r="AJ29">
         <v>1</v>
       </c>
@@ -1343,6 +2733,9 @@
       <c r="BN29">
         <v>1</v>
       </c>
+      <c r="BX29">
+        <v>3</v>
+      </c>
       <c r="CA29">
         <v>1</v>
       </c>
@@ -1424,6 +2817,9 @@
       <c r="EF29">
         <v>1</v>
       </c>
+      <c r="EN29">
+        <v>4</v>
+      </c>
       <c r="ES29">
         <v>1</v>
       </c>
@@ -1466,8 +2862,263 @@
       <c r="FF29">
         <v>1</v>
       </c>
+      <c r="FG29">
+        <v>1</v>
+      </c>
+      <c r="FH29">
+        <v>1</v>
+      </c>
+      <c r="FI29">
+        <v>1</v>
+      </c>
+      <c r="FJ29">
+        <v>1</v>
+      </c>
+      <c r="FK29">
+        <v>1</v>
+      </c>
+      <c r="FL29">
+        <v>1</v>
+      </c>
+      <c r="FM29">
+        <v>1</v>
+      </c>
+      <c r="FN29">
+        <v>1</v>
+      </c>
+      <c r="FO29">
+        <v>1</v>
+      </c>
+      <c r="FP29">
+        <v>1</v>
+      </c>
+      <c r="FQ29">
+        <v>1</v>
+      </c>
+      <c r="FR29">
+        <v>1</v>
+      </c>
+      <c r="FS29">
+        <v>1</v>
+      </c>
+      <c r="FT29">
+        <v>1</v>
+      </c>
+      <c r="FU29">
+        <v>1</v>
+      </c>
+      <c r="FV29">
+        <v>1</v>
+      </c>
+      <c r="FW29">
+        <v>1</v>
+      </c>
+      <c r="FX29">
+        <v>1</v>
+      </c>
+      <c r="FY29">
+        <v>1</v>
+      </c>
+      <c r="FZ29">
+        <v>1</v>
+      </c>
+      <c r="GA29">
+        <v>1</v>
+      </c>
+      <c r="GB29">
+        <v>1</v>
+      </c>
+      <c r="GC29">
+        <v>1</v>
+      </c>
+      <c r="GD29">
+        <v>1</v>
+      </c>
+      <c r="GE29">
+        <v>1</v>
+      </c>
+      <c r="GF29">
+        <v>1</v>
+      </c>
+      <c r="GG29">
+        <v>1</v>
+      </c>
+      <c r="GH29">
+        <v>1</v>
+      </c>
+      <c r="GI29">
+        <v>1</v>
+      </c>
+      <c r="GJ29">
+        <v>1</v>
+      </c>
+      <c r="GK29">
+        <v>1</v>
+      </c>
+      <c r="GL29">
+        <v>1</v>
+      </c>
+      <c r="GM29">
+        <v>1</v>
+      </c>
+      <c r="GN29">
+        <v>1</v>
+      </c>
+      <c r="GO29">
+        <v>1</v>
+      </c>
+      <c r="GP29">
+        <v>1</v>
+      </c>
+      <c r="GQ29">
+        <v>1</v>
+      </c>
+      <c r="GR29">
+        <v>1</v>
+      </c>
+      <c r="GS29">
+        <v>1</v>
+      </c>
+      <c r="GT29">
+        <v>1</v>
+      </c>
+      <c r="GU29">
+        <v>1</v>
+      </c>
+      <c r="GV29">
+        <v>1</v>
+      </c>
+      <c r="GW29">
+        <v>1</v>
+      </c>
+      <c r="GX29">
+        <v>1</v>
+      </c>
+      <c r="GY29">
+        <v>1</v>
+      </c>
+      <c r="GZ29">
+        <v>1</v>
+      </c>
+      <c r="HA29">
+        <v>1</v>
+      </c>
+      <c r="HB29">
+        <v>1</v>
+      </c>
+      <c r="HC29">
+        <v>1</v>
+      </c>
+      <c r="HD29">
+        <v>1</v>
+      </c>
+      <c r="HE29">
+        <v>1</v>
+      </c>
+      <c r="HF29">
+        <v>1</v>
+      </c>
+      <c r="HG29">
+        <v>1</v>
+      </c>
+      <c r="HH29">
+        <v>1</v>
+      </c>
+      <c r="HI29">
+        <v>1</v>
+      </c>
+      <c r="HJ29">
+        <v>1</v>
+      </c>
+      <c r="HK29">
+        <v>1</v>
+      </c>
+      <c r="HL29">
+        <v>1</v>
+      </c>
+      <c r="HM29">
+        <v>1</v>
+      </c>
+      <c r="HN29">
+        <v>1</v>
+      </c>
+      <c r="HO29">
+        <v>1</v>
+      </c>
+      <c r="HP29">
+        <v>1</v>
+      </c>
+      <c r="HQ29">
+        <v>1</v>
+      </c>
+      <c r="HR29">
+        <v>1</v>
+      </c>
+      <c r="HS29">
+        <v>1</v>
+      </c>
+      <c r="HT29">
+        <v>1</v>
+      </c>
+      <c r="HU29">
+        <v>1</v>
+      </c>
+      <c r="HV29">
+        <v>1</v>
+      </c>
+      <c r="HW29">
+        <v>1</v>
+      </c>
+      <c r="HX29">
+        <v>1</v>
+      </c>
+      <c r="HY29">
+        <v>1</v>
+      </c>
+      <c r="HZ29">
+        <v>1</v>
+      </c>
+      <c r="IA29">
+        <v>1</v>
+      </c>
+      <c r="IB29">
+        <v>1</v>
+      </c>
+      <c r="IE29">
+        <v>3</v>
+      </c>
+      <c r="IG29">
+        <v>1</v>
+      </c>
+      <c r="IH29">
+        <v>1</v>
+      </c>
+      <c r="II29">
+        <v>1</v>
+      </c>
+      <c r="IQ29">
+        <v>3</v>
+      </c>
+      <c r="IX29">
+        <v>1</v>
+      </c>
+      <c r="IY29">
+        <v>1</v>
+      </c>
+      <c r="IZ29">
+        <v>1</v>
+      </c>
+      <c r="JA29">
+        <v>1</v>
+      </c>
+      <c r="JB29">
+        <v>1</v>
+      </c>
+      <c r="JC29">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:162" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>1</v>
       </c>
@@ -1952,19 +3603,339 @@
         <v>1</v>
       </c>
       <c r="FF30">
+        <v>1</v>
+      </c>
+      <c r="FG30">
+        <v>1</v>
+      </c>
+      <c r="FH30">
+        <v>1</v>
+      </c>
+      <c r="FI30">
+        <v>1</v>
+      </c>
+      <c r="FJ30">
+        <v>1</v>
+      </c>
+      <c r="FK30">
+        <v>1</v>
+      </c>
+      <c r="FL30">
+        <v>1</v>
+      </c>
+      <c r="FM30">
+        <v>1</v>
+      </c>
+      <c r="FN30">
+        <v>1</v>
+      </c>
+      <c r="FO30">
+        <v>1</v>
+      </c>
+      <c r="FP30">
+        <v>1</v>
+      </c>
+      <c r="FQ30">
+        <v>1</v>
+      </c>
+      <c r="FR30">
+        <v>1</v>
+      </c>
+      <c r="FS30">
+        <v>1</v>
+      </c>
+      <c r="FT30">
+        <v>1</v>
+      </c>
+      <c r="FU30">
+        <v>1</v>
+      </c>
+      <c r="FV30">
+        <v>1</v>
+      </c>
+      <c r="FW30">
+        <v>1</v>
+      </c>
+      <c r="FX30">
+        <v>1</v>
+      </c>
+      <c r="FY30">
+        <v>1</v>
+      </c>
+      <c r="FZ30">
+        <v>1</v>
+      </c>
+      <c r="GA30">
+        <v>1</v>
+      </c>
+      <c r="GB30">
+        <v>1</v>
+      </c>
+      <c r="GC30">
+        <v>1</v>
+      </c>
+      <c r="GD30">
+        <v>1</v>
+      </c>
+      <c r="GE30">
+        <v>1</v>
+      </c>
+      <c r="GF30">
+        <v>1</v>
+      </c>
+      <c r="GG30">
+        <v>1</v>
+      </c>
+      <c r="GH30">
+        <v>1</v>
+      </c>
+      <c r="GI30">
+        <v>1</v>
+      </c>
+      <c r="GJ30">
+        <v>1</v>
+      </c>
+      <c r="GK30">
+        <v>1</v>
+      </c>
+      <c r="GL30">
+        <v>1</v>
+      </c>
+      <c r="GM30">
+        <v>1</v>
+      </c>
+      <c r="GN30">
+        <v>1</v>
+      </c>
+      <c r="GO30">
+        <v>1</v>
+      </c>
+      <c r="GP30">
+        <v>1</v>
+      </c>
+      <c r="GQ30">
+        <v>1</v>
+      </c>
+      <c r="GR30">
+        <v>1</v>
+      </c>
+      <c r="GS30">
+        <v>1</v>
+      </c>
+      <c r="GT30">
+        <v>1</v>
+      </c>
+      <c r="GU30">
+        <v>1</v>
+      </c>
+      <c r="GV30">
+        <v>1</v>
+      </c>
+      <c r="GW30">
+        <v>1</v>
+      </c>
+      <c r="GX30">
+        <v>1</v>
+      </c>
+      <c r="GY30">
+        <v>1</v>
+      </c>
+      <c r="GZ30">
+        <v>1</v>
+      </c>
+      <c r="HA30">
+        <v>1</v>
+      </c>
+      <c r="HB30">
+        <v>1</v>
+      </c>
+      <c r="HC30">
+        <v>1</v>
+      </c>
+      <c r="HD30">
+        <v>1</v>
+      </c>
+      <c r="HE30">
+        <v>1</v>
+      </c>
+      <c r="HF30">
+        <v>1</v>
+      </c>
+      <c r="HG30">
+        <v>1</v>
+      </c>
+      <c r="HH30">
+        <v>1</v>
+      </c>
+      <c r="HI30">
+        <v>1</v>
+      </c>
+      <c r="HJ30">
+        <v>1</v>
+      </c>
+      <c r="HK30">
+        <v>1</v>
+      </c>
+      <c r="HL30">
+        <v>1</v>
+      </c>
+      <c r="HM30">
+        <v>1</v>
+      </c>
+      <c r="HN30">
+        <v>1</v>
+      </c>
+      <c r="HO30">
+        <v>1</v>
+      </c>
+      <c r="HP30">
+        <v>1</v>
+      </c>
+      <c r="HQ30">
+        <v>1</v>
+      </c>
+      <c r="HR30">
+        <v>1</v>
+      </c>
+      <c r="HS30">
+        <v>1</v>
+      </c>
+      <c r="HT30">
+        <v>1</v>
+      </c>
+      <c r="HU30">
+        <v>1</v>
+      </c>
+      <c r="HV30">
+        <v>1</v>
+      </c>
+      <c r="HW30">
+        <v>1</v>
+      </c>
+      <c r="HX30">
+        <v>1</v>
+      </c>
+      <c r="HY30">
+        <v>1</v>
+      </c>
+      <c r="HZ30">
+        <v>1</v>
+      </c>
+      <c r="IA30">
+        <v>1</v>
+      </c>
+      <c r="IB30">
+        <v>1</v>
+      </c>
+      <c r="IC30">
+        <v>1</v>
+      </c>
+      <c r="ID30">
+        <v>1</v>
+      </c>
+      <c r="IE30">
+        <v>1</v>
+      </c>
+      <c r="IF30">
+        <v>1</v>
+      </c>
+      <c r="IG30">
+        <v>1</v>
+      </c>
+      <c r="IH30">
+        <v>1</v>
+      </c>
+      <c r="II30">
+        <v>1</v>
+      </c>
+      <c r="IJ30">
+        <v>1</v>
+      </c>
+      <c r="IK30">
+        <v>1</v>
+      </c>
+      <c r="IL30">
+        <v>1</v>
+      </c>
+      <c r="IM30">
+        <v>1</v>
+      </c>
+      <c r="IN30">
+        <v>1</v>
+      </c>
+      <c r="IO30">
+        <v>1</v>
+      </c>
+      <c r="IP30">
+        <v>1</v>
+      </c>
+      <c r="IQ30">
+        <v>1</v>
+      </c>
+      <c r="IR30">
+        <v>1</v>
+      </c>
+      <c r="IS30">
+        <v>1</v>
+      </c>
+      <c r="IT30">
+        <v>1</v>
+      </c>
+      <c r="IU30">
+        <v>1</v>
+      </c>
+      <c r="IV30">
+        <v>1</v>
+      </c>
+      <c r="IW30">
+        <v>1</v>
+      </c>
+      <c r="IX30">
+        <v>1</v>
+      </c>
+      <c r="IY30">
+        <v>1</v>
+      </c>
+      <c r="IZ30">
+        <v>1</v>
+      </c>
+      <c r="JA30">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="1">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="1">
       <formula>NOT(ISERROR(SEARCH("1",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="1">
+      <formula>NOT(ISERROR(SEARCH("1",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="3">
+      <formula>NOT(ISERROR(SEARCH("3",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="4">
+      <formula>NOT(ISERROR(SEARCH("4",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="5">
+      <formula>NOT(ISERROR(SEARCH("5",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="10">
+      <formula>NOT(ISERROR(SEARCH("10",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="9">
+      <formula>NOT(ISERROR(SEARCH("9",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:FF30">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="2">
+    <cfRule type="containsText" dxfId="1" priority="8" operator="containsText" text="2">
       <formula>NOT(ISERROR(SEARCH("2",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="KG16">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="9">
+      <formula>NOT(ISERROR(SEARCH("9",KG16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1976,20 +3947,20 @@
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId4" name="Button 1">
+            <control shapeId="1026" r:id="rId4" name="Button 2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!Sheet1.ExportMap">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
-                    <xdr:col>44</xdr:col>
-                    <xdr:colOff>171450</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
+                    <xdr:col>42</xdr:col>
+                    <xdr:colOff>123825</xdr:colOff>
+                    <xdr:row>32</xdr:row>
+                    <xdr:rowOff>104775</xdr:rowOff>
                   </from>
                   <to>
-                    <xdr:col>48</xdr:col>
-                    <xdr:colOff>142875</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>47625</xdr:rowOff>
+                    <xdr:col>54</xdr:col>
+                    <xdr:colOff>228600</xdr:colOff>
+                    <xdr:row>36</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>

--- a/Rescource/Stage1.xlsx
+++ b/Rescource/Stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5138C30-AA2F-484A-AD4F-408F6D7370C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B56C44-999B-46C5-9211-F981B9948C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7800" yWindow="0" windowWidth="21000" windowHeight="14880" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
+    <workbookView xWindow="5175" yWindow="-15045" windowWidth="21000" windowHeight="14880" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1262,6 +1262,12 @@
       <c r="BL18">
         <v>1</v>
       </c>
+      <c r="FY18">
+        <v>1</v>
+      </c>
+      <c r="FZ18">
+        <v>1</v>
+      </c>
       <c r="GA18">
         <v>1</v>
       </c>

--- a/Rescource/Stage1.xlsx
+++ b/Rescource/Stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B56C44-999B-46C5-9211-F981B9948C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3B7324-0562-4848-9E82-0102468FDFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5175" yWindow="-15045" windowWidth="21000" windowHeight="14880" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
+    <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -571,8 +571,11 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="GX4">
-        <v>5</v>
+      <c r="GU4">
+        <v>3</v>
+      </c>
+      <c r="GY4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -754,8 +757,11 @@
       <c r="A13">
         <v>1</v>
       </c>
-      <c r="HD13">
-        <v>5</v>
+      <c r="HA13">
+        <v>3</v>
+      </c>
+      <c r="HE13">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -804,13 +810,22 @@
       <c r="HD14">
         <v>1</v>
       </c>
-      <c r="IL14">
+      <c r="II14">
         <v>3</v>
       </c>
-      <c r="IV14">
+      <c r="IO14">
         <v>3</v>
       </c>
-      <c r="JH14">
+      <c r="IR14">
+        <v>3</v>
+      </c>
+      <c r="IY14">
+        <v>3</v>
+      </c>
+      <c r="JC14">
+        <v>3</v>
+      </c>
+      <c r="JI14">
         <v>3</v>
       </c>
     </row>
@@ -845,8 +860,11 @@
       <c r="HD15">
         <v>1</v>
       </c>
-      <c r="HV15">
-        <v>4</v>
+      <c r="HM15">
+        <v>3</v>
+      </c>
+      <c r="HX15">
+        <v>3</v>
       </c>
       <c r="IJ15">
         <v>1</v>
@@ -925,9 +943,6 @@
       <c r="GR16">
         <v>1</v>
       </c>
-      <c r="GU16">
-        <v>4</v>
-      </c>
       <c r="GV16">
         <v>1</v>
       </c>
@@ -975,13 +990,19 @@
       </c>
       <c r="HW16">
         <v>1</v>
+      </c>
+      <c r="IG16">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:305" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1</v>
       </c>
-      <c r="BK17">
+      <c r="BF17">
+        <v>3</v>
+      </c>
+      <c r="BM17">
         <v>3</v>
       </c>
       <c r="GA17">
@@ -1659,7 +1680,10 @@
       <c r="AD20">
         <v>1</v>
       </c>
-      <c r="FR20">
+      <c r="FO20">
+        <v>3</v>
+      </c>
+      <c r="FW20">
         <v>3</v>
       </c>
       <c r="GW20">
@@ -1766,7 +1790,7 @@
       <c r="HF21">
         <v>1</v>
       </c>
-      <c r="JM21">
+      <c r="JK21">
         <v>3</v>
       </c>
       <c r="JN21">
@@ -1816,8 +1840,11 @@
       <c r="BU22">
         <v>1</v>
       </c>
-      <c r="DJ22">
-        <v>5</v>
+      <c r="DF22">
+        <v>3</v>
+      </c>
+      <c r="DL22">
+        <v>3</v>
       </c>
       <c r="GY22">
         <v>1</v>
@@ -1863,8 +1890,11 @@
       <c r="A23">
         <v>1</v>
       </c>
-      <c r="CM23">
-        <v>4</v>
+      <c r="CH23">
+        <v>3</v>
+      </c>
+      <c r="CO23">
+        <v>3</v>
       </c>
       <c r="DG23">
         <v>1</v>
@@ -2062,10 +2092,7 @@
       <c r="GL25">
         <v>1</v>
       </c>
-      <c r="II25">
-        <v>4</v>
-      </c>
-      <c r="JE25">
+      <c r="JC25">
         <v>3</v>
       </c>
       <c r="JF25">
@@ -2118,9 +2145,12 @@
       <c r="AV26">
         <v>1</v>
       </c>
-      <c r="BE26">
+      <c r="BD26">
         <v>3</v>
       </c>
+      <c r="BG26">
+        <v>3</v>
+      </c>
       <c r="CE26">
         <v>1</v>
       </c>
@@ -2187,7 +2217,10 @@
       <c r="GN26">
         <v>1</v>
       </c>
-      <c r="GP26">
+      <c r="GO26">
+        <v>3</v>
+      </c>
+      <c r="GQ26">
         <v>3</v>
       </c>
       <c r="HK26">
@@ -2372,11 +2405,8 @@
       <c r="HN27">
         <v>1</v>
       </c>
-      <c r="HP27">
-        <v>4</v>
-      </c>
-      <c r="HW27">
-        <v>5</v>
+      <c r="HR27">
+        <v>3</v>
       </c>
       <c r="HY27">
         <v>1</v>
@@ -2563,12 +2593,9 @@
       <c r="EF28">
         <v>1</v>
       </c>
-      <c r="EZ28">
+      <c r="ER28">
         <v>3</v>
       </c>
-      <c r="FW28">
-        <v>3</v>
-      </c>
       <c r="GF28">
         <v>1</v>
       </c>
@@ -2589,9 +2616,6 @@
       </c>
       <c r="GR28">
         <v>1</v>
-      </c>
-      <c r="HG28">
-        <v>3</v>
       </c>
       <c r="HK28">
         <v>1</v>
@@ -2685,9 +2709,6 @@
       <c r="G29">
         <v>1</v>
       </c>
-      <c r="X29">
-        <v>3</v>
-      </c>
       <c r="AJ29">
         <v>1</v>
       </c>
@@ -2739,9 +2760,6 @@
       <c r="BN29">
         <v>1</v>
       </c>
-      <c r="BX29">
-        <v>3</v>
-      </c>
       <c r="CA29">
         <v>1</v>
       </c>
@@ -2823,9 +2841,6 @@
       <c r="EF29">
         <v>1</v>
       </c>
-      <c r="EN29">
-        <v>4</v>
-      </c>
       <c r="ES29">
         <v>1</v>
       </c>
@@ -3090,9 +3105,6 @@
       <c r="IB29">
         <v>1</v>
       </c>
-      <c r="IE29">
-        <v>3</v>
-      </c>
       <c r="IG29">
         <v>1</v>
       </c>
@@ -3101,9 +3113,6 @@
       </c>
       <c r="II29">
         <v>1</v>
-      </c>
-      <c r="IQ29">
-        <v>3</v>
       </c>
       <c r="IX29">
         <v>1</v>

--- a/Rescource/Stage1.xlsx
+++ b/Rescource/Stage1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3B7324-0562-4848-9E82-0102468FDFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18733E43-9B51-4F5E-A7AE-247D4CBDB581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
   </bookViews>
@@ -1949,6 +1949,12 @@
       <c r="A24">
         <v>1</v>
       </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="Q24">
+        <v>3</v>
+      </c>
       <c r="AN24">
         <v>1</v>
       </c>

--- a/Rescource/Stage1.xlsx
+++ b/Rescource/Stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\Rescource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18733E43-9B51-4F5E-A7AE-247D4CBDB581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620ADD30-2034-4017-BD75-7487A0C51A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
+    <workbookView xWindow="75" yWindow="-14820" windowWidth="26850" windowHeight="14655" xr2:uid="{FDCFA8C7-98AB-45DA-A2E8-3FAE977877BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -577,6 +577,12 @@
       <c r="GY4">
         <v>3</v>
       </c>
+      <c r="HD4">
+        <v>3</v>
+      </c>
+      <c r="HH4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
@@ -628,6 +634,9 @@
       <c r="A7">
         <v>1</v>
       </c>
+      <c r="GR7">
+        <v>3</v>
+      </c>
       <c r="GV7">
         <v>1</v>
       </c>
@@ -636,6 +645,9 @@
       </c>
       <c r="GX7">
         <v>1</v>
+      </c>
+      <c r="HB7">
+        <v>3</v>
       </c>
       <c r="HE7">
         <v>1</v>
@@ -692,6 +704,12 @@
       <c r="HA9">
         <v>1</v>
       </c>
+      <c r="HE9">
+        <v>3</v>
+      </c>
+      <c r="HI9">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:296" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
@@ -729,6 +747,12 @@
       <c r="A11">
         <v>1</v>
       </c>
+      <c r="CJ11">
+        <v>3</v>
+      </c>
+      <c r="CP11">
+        <v>3</v>
+      </c>
       <c r="HF11">
         <v>1</v>
       </c>
@@ -743,6 +767,24 @@
       <c r="A12">
         <v>1</v>
       </c>
+      <c r="CE12">
+        <v>1</v>
+      </c>
+      <c r="CK12">
+        <v>1</v>
+      </c>
+      <c r="CL12">
+        <v>1</v>
+      </c>
+      <c r="CM12">
+        <v>1</v>
+      </c>
+      <c r="CN12">
+        <v>1</v>
+      </c>
+      <c r="CO12">
+        <v>1</v>
+      </c>
       <c r="HF12">
         <v>1</v>
       </c>
@@ -757,6 +799,33 @@
       <c r="A13">
         <v>1</v>
       </c>
+      <c r="AK13">
+        <v>3</v>
+      </c>
+      <c r="AQ13">
+        <v>3</v>
+      </c>
+      <c r="CL13">
+        <v>1</v>
+      </c>
+      <c r="CM13">
+        <v>1</v>
+      </c>
+      <c r="CN13">
+        <v>1</v>
+      </c>
+      <c r="GO13">
+        <v>3</v>
+      </c>
+      <c r="GS13">
+        <v>3</v>
+      </c>
+      <c r="GU13">
+        <v>3</v>
+      </c>
+      <c r="GY13">
+        <v>3</v>
+      </c>
       <c r="HA13">
         <v>3</v>
       </c>
@@ -833,6 +902,12 @@
       <c r="A15">
         <v>1</v>
       </c>
+      <c r="AD15">
+        <v>3</v>
+      </c>
+      <c r="AI15">
+        <v>3</v>
+      </c>
       <c r="GP15">
         <v>1</v>
       </c>
@@ -934,6 +1009,12 @@
       <c r="AH16">
         <v>1</v>
       </c>
+      <c r="CB16">
+        <v>1</v>
+      </c>
+      <c r="FZ16">
+        <v>3</v>
+      </c>
       <c r="GP16">
         <v>1</v>
       </c>
@@ -999,6 +1080,12 @@
       <c r="A17">
         <v>1</v>
       </c>
+      <c r="AU17">
+        <v>3</v>
+      </c>
+      <c r="BB17">
+        <v>3</v>
+      </c>
       <c r="BF17">
         <v>3</v>
       </c>
@@ -1543,6 +1630,15 @@
       <c r="A19">
         <v>1</v>
       </c>
+      <c r="AA19">
+        <v>3</v>
+      </c>
+      <c r="AE19">
+        <v>3</v>
+      </c>
+      <c r="BX19">
+        <v>1</v>
+      </c>
       <c r="GV19">
         <v>1</v>
       </c>
@@ -1742,6 +1838,18 @@
       <c r="A21">
         <v>1</v>
       </c>
+      <c r="R21">
+        <v>3</v>
+      </c>
+      <c r="X21">
+        <v>3</v>
+      </c>
+      <c r="BR21">
+        <v>3</v>
+      </c>
+      <c r="BV21">
+        <v>3</v>
+      </c>
       <c r="FP21">
         <v>1</v>
       </c>
@@ -1890,6 +1998,12 @@
       <c r="A23">
         <v>1</v>
       </c>
+      <c r="AM23">
+        <v>3</v>
+      </c>
+      <c r="AR23">
+        <v>3</v>
+      </c>
       <c r="CH23">
         <v>3</v>
       </c>
@@ -1985,6 +2099,18 @@
       <c r="CN24">
         <v>1</v>
       </c>
+      <c r="CX24">
+        <v>3</v>
+      </c>
+      <c r="DD24">
+        <v>3</v>
+      </c>
+      <c r="FG24">
+        <v>3</v>
+      </c>
+      <c r="FN24">
+        <v>3</v>
+      </c>
       <c r="HA24">
         <v>1</v>
       </c>
@@ -2044,6 +2170,12 @@
       <c r="AQ25">
         <v>1</v>
       </c>
+      <c r="AW25">
+        <v>3</v>
+      </c>
+      <c r="CD25">
+        <v>3</v>
+      </c>
       <c r="CI25">
         <v>1</v>
       </c>
@@ -2062,6 +2194,9 @@
       <c r="CN25">
         <v>1</v>
       </c>
+      <c r="CS25">
+        <v>3</v>
+      </c>
       <c r="CY25">
         <v>1</v>
       </c>
@@ -2077,6 +2212,12 @@
       <c r="DC25">
         <v>1</v>
       </c>
+      <c r="DR25">
+        <v>3</v>
+      </c>
+      <c r="DX25">
+        <v>3</v>
+      </c>
       <c r="FH25">
         <v>1</v>
       </c>
@@ -2097,6 +2238,12 @@
       </c>
       <c r="GL25">
         <v>1</v>
+      </c>
+      <c r="IF25">
+        <v>3</v>
+      </c>
+      <c r="IJ25">
+        <v>3</v>
       </c>
       <c r="JC25">
         <v>3</v>
@@ -2124,6 +2271,9 @@
       <c r="A26">
         <v>1</v>
       </c>
+      <c r="AI26">
+        <v>3</v>
+      </c>
       <c r="AN26">
         <v>1</v>
       </c>
@@ -2157,6 +2307,12 @@
       <c r="BG26">
         <v>3</v>
       </c>
+      <c r="BL26">
+        <v>3</v>
+      </c>
+      <c r="BO26">
+        <v>3</v>
+      </c>
       <c r="CE26">
         <v>1</v>
       </c>
@@ -2214,6 +2370,12 @@
       <c r="DW26">
         <v>1</v>
       </c>
+      <c r="ED26">
+        <v>3</v>
+      </c>
+      <c r="EG26">
+        <v>3</v>
+      </c>
       <c r="GJ26">
         <v>1</v>
       </c>
@@ -2231,6 +2393,12 @@
       </c>
       <c r="HK26">
         <v>1</v>
+      </c>
+      <c r="HO26">
+        <v>3</v>
+      </c>
+      <c r="HX26">
+        <v>3</v>
       </c>
       <c r="IB26">
         <v>1</v>
@@ -2336,6 +2504,9 @@
       <c r="BN27">
         <v>1</v>
       </c>
+      <c r="BZ27">
+        <v>3</v>
+      </c>
       <c r="CE27">
         <v>1</v>
       </c>
@@ -2378,6 +2549,9 @@
       <c r="CR27">
         <v>1</v>
       </c>
+      <c r="CW27">
+        <v>3</v>
+      </c>
       <c r="EE27">
         <v>1</v>
       </c>
@@ -2412,6 +2586,9 @@
         <v>1</v>
       </c>
       <c r="HR27">
+        <v>3</v>
+      </c>
+      <c r="HU27">
         <v>3</v>
       </c>
       <c r="HY27">
@@ -2592,6 +2769,12 @@
       </c>
       <c r="CV28">
         <v>1</v>
+      </c>
+      <c r="DH28">
+        <v>3</v>
+      </c>
+      <c r="DL28">
+        <v>3</v>
       </c>
       <c r="EE28">
         <v>1</v>
